--- a/dados_teste/Safras.xlsx
+++ b/dados_teste/Safras.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-24375" yWindow="1680" windowWidth="21600" windowHeight="11235" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planilha1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Planilha1'!$A$1:$D$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Planilha1'!$A$1:$D$46</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>8.85</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>75.56999999999999</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>668.8200000000001</v>
+        <v>666.45</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>81.73999999999999</v>
+        <v>84.42</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4.28</v>
+        <v>4.2</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>350.21</v>
+        <v>354.83</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1569,9 +1569,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D52">
+  <autoFilter ref="A1:D46">
     <sortState ref="A2:D46">
-      <sortCondition ref="A1:A52"/>
+      <sortCondition ref="A1:A46"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
